--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_CBQ.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_CBQ.xlsx
@@ -1423,7 +1423,11 @@
           <t>CBQ_T._JERVIS</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322711</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>T. Jervis</t>
@@ -3657,7 +3661,11 @@
           <t>CBQ_T._JERVIS</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322711</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>T. Jervis</t>
@@ -7083,7 +7091,11 @@
           <t>CBQ_T._JERVIS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>322711</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>T. Jervis</t>
@@ -9673,7 +9685,11 @@
           <t>CBQ_T._JERVIS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322711</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>T. Jervis</t>
@@ -10735,7 +10751,11 @@
           <t>CBQ_T._JERVIS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>322711</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>T. Jervis</t>
@@ -10991,7 +11011,11 @@
           <t>CBQ_T._JERVIS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322711</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>T. Jervis</t>
